--- a/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-resultats-examens-biologie-medicale</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-resultats-examens-biologie-medicale|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-resultat-examens-de-biologie-medicale</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-resultat-examens-de-biologie-medicale</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale</t>
@@ -214,7 +214,7 @@
     <t>FRCDAResultatExamensDeBiologie.entryRelationship:frCommentaireER</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-observation-laboratory-report-results-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-laboratory-report-results-document|0.1.0</t>
   </si>
   <si>
     <t>FRObservationLaboratoryReportResultsDocument</t>

--- a/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="83">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-resultats-examens-biologie-medicale|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMResultatsExamensBiologieMedicale|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-resultat-examens-de-biologie-medicale</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-resultats-examens-de-biologie-medicale|0.1.0</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale</t>
@@ -115,31 +115,34 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>Act</t>
+  </si>
+  <si>
     <t>FRCDAResultatExamensDeBiologie</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale.code</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.code</t>
+    <t>Act.code</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale.statut</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.statusCode</t>
+    <t>Act.statusCode</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale.dateResultat</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.effectiveTime</t>
+    <t>Act.effectiveTime</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale.choice:FRLMSujetNonHumain</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.subject</t>
+    <t>Act.subject</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale.choice:FRLMPatientSujetNonHumain</t>
@@ -148,19 +151,19 @@
     <t>FRLMResultatsExamensBiologieMedicale.laboratoireExecutant</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.performer</t>
+    <t>Act.performer</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale.auteur</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.author</t>
+    <t>Act.author</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale.valideur</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.participant</t>
+    <t>Act.participant</t>
   </si>
   <si>
     <t>Authenticator (CDA participant) : participant/@typeCode='AUTHEN'</t>
@@ -181,82 +184,85 @@
     <t>FRLMResultatsExamensBiologieMedicale.prelevement</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.entryRelationship:frPrelevement</t>
+    <t>Act.entryRelationship:frPrelevement</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale.batterieExamensDeBiologieMedicale</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.entryRelationship:frBatterieExamensDeBiologieMedicale</t>
+    <t>Act.entryRelationship:frBatterieExamensDeBiologieMedicale</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale.isolatMicrobiologique</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.entryRelationship:frIsolatMicrobiologique</t>
+    <t>Act.entryRelationship:frIsolatMicrobiologique</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale.resultatElementCliniquePertinent</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.entryRelationship:frResultatExamensDeBiologieElementCliniquePertinent</t>
+    <t>Act.entryRelationship:frResultatExamensDeBiologieElementCliniquePertinent</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale.imageIllustrative</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.entryRelationship:frImageIllustrative</t>
+    <t>Act.entryRelationship:frImageIllustrative</t>
   </si>
   <si>
     <t>FRLMResultatsExamensBiologieMedicale.commentaire</t>
   </si>
   <si>
-    <t>FRCDAResultatExamensDeBiologie.entryRelationship:frCommentaireER</t>
+    <t>Act.entryRelationship:frCommentaireER</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-laboratory-report-results-document|0.1.0</t>
   </si>
   <si>
+    <t>Observation</t>
+  </si>
+  <si>
     <t>FRObservationLaboratoryReportResultsDocument</t>
   </si>
   <si>
-    <t>FRObservationLaboratoryReportResultsDocument.code</t>
-  </si>
-  <si>
-    <t>FRObservationLaboratoryReportResultsDocument.status</t>
-  </si>
-  <si>
-    <t>FRObservationLaboratoryReportResultsDocument.effectivePeriod</t>
-  </si>
-  <si>
-    <t>FRObservationLaboratoryReportResultsDocument.subject</t>
-  </si>
-  <si>
-    <t>FRObservationLaboratoryReportResultsDocument.performer.extension:laboratoireExecutant</t>
-  </si>
-  <si>
-    <t>FRObservationLaboratoryReportResultsDocument.performer.extension:author</t>
-  </si>
-  <si>
-    <t>FRObservationLaboratoryReportResultsDocument.performer.extension:validateurResultat</t>
-  </si>
-  <si>
-    <t>FRObservationLaboratoryReportResultsDocument.performer.extension:responsableExamen</t>
-  </si>
-  <si>
-    <t>FRObservationLaboratoryReportResultsDocument.performer.extension:dispositifAuto</t>
-  </si>
-  <si>
-    <t>FRObservationLaboratoryReportResultsDocument.specimen</t>
-  </si>
-  <si>
-    <t>FRObservationLaboratoryReportResultsDocument.note</t>
-  </si>
-  <si>
-    <t>FRObservationLaboratoryReportResultsDocument.hasMember:FRObservationLaboratoryReportResultsDocument</t>
-  </si>
-  <si>
-    <t>FRObservationLaboratoryReportResultsDocument.derivedFrom:FRMediaDocument</t>
+    <t>Observation.code</t>
+  </si>
+  <si>
+    <t>Observation.status</t>
+  </si>
+  <si>
+    <t>Observation.effectivePeriod</t>
+  </si>
+  <si>
+    <t>Observation.subject</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:laboratoireExecutant</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:validateurResultat</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:responsableExamen</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:dispositifAuto</t>
+  </si>
+  <si>
+    <t>Observation.specimen</t>
+  </si>
+  <si>
+    <t>Observation.note</t>
+  </si>
+  <si>
+    <t>Observation.hasMember:FRObservationLaboratoryReportResultsDocument</t>
+  </si>
+  <si>
+    <t>Observation.derivedFrom:FRMediaDocument</t>
   </si>
 </sst>
 </file>
@@ -556,219 +562,221 @@
       <c r="D3" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2"/>
     </row>
@@ -810,7 +818,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -825,208 +833,210 @@
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>69</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
     </row>

--- a/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
+++ b/main/ig/FRLaboratoryResultsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
